--- a/www/download/COUNTRY.BEL.zdW16.xlsx
+++ b/www/download/COUNTRY.BEL.zdW16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Bélgica</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>1.0827197921178</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>1.11656989727557</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>1.0575296108291</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>0.884016973125884</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>0.803923144947343</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>0.803793907242183</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.796431984708506</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>0.729660707770887</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.67990209409845</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>0.71694866647548</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>0.75431847325941</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>0.718390804597701</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>0.778331257783313</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>0.75295534974776</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.752709314500807</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>4.109</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>4.165</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>4.157</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>4.154</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>4.194</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>4.255</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>4.303</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>4.374</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>4.453</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>4.446</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>4.474</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>4.536</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>4.552</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>4.534</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>4.55</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>3.407</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3.47</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>3.468</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>3.465</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>3.503</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>3.561</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>3.604</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>3.669</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>3.737</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>3.724</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>3.748</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>3.801</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>3.809</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>3.785</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>3.795</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>5976.432</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>6038.386</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>6005.793</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>6003.316</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>6066.013</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>6138.331</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>6217.963</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>6338.011</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>6436.824</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>6338.167</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>6370.07</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>6509.268</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>6537.069</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>6506.505</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>6531.333</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4972.022</t>
+          <t>9236587537.27817</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5046.563</t>
+          <t>8908027640.06044</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>5019.687</t>
+          <t>8684240796.7507</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>5016.187</t>
+          <t>9243698077.57196</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>5074.917</t>
+          <t>9900790775.06646</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>5141.645</t>
+          <t>9565632438.65398</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>5207.967</t>
+          <t>10421244147.6864</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>5311.215</t>
+          <t>11096570673.0336</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>5394.065</t>
+          <t>11434523174.4589</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>5290.562</t>
+          <t>10528305994.9496</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>5320.788</t>
+          <t>11912810005.1682</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>5434.913</t>
+          <t>13978720457.8264</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>5449.255</t>
+          <t>12821728444.4877</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>5407.5</t>
+          <t>12719636518.1426</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>5424.248</t>
+          <t>13889969244.0632</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>6323438676.76068</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>6525601410.86441</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>6758446507.88281</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>7655082694.36288</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>8420635386.03747</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>8148435522.95173</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>7764940109.69111</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>7712021615.17368</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>7598027223.93953</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>6906507918.36992</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>5168672544.26916</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>5336931030.93052</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>5046717478.78526</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>5399961122.63479</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>5687285244.76614</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1049855.83044103</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1035844.57999759</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>964008.817250208</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>850097.493529136</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>795349.987492812</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>733621.509894001</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>713752.368229655</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>646128.643286883</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>605646.068216719</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>669145.717943859</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>728412.398918248</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>721250.056612785</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>711395.891708663</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>688961.946799259</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>732066.143485683</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>24477.1224255996</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>24230.1895488714</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>23956.2826510716</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>25863.4930609535</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>28555.004467801</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>30605.166609011</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>32773.2228654555</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>37248.3163992203</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>41063.7547227556</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>36669.349360797</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>40676.1629590996</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>44506.7593570651</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>43422.4781554925</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>42902.44863766</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>43062.0332928285</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>83788.2240435774</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>79624.5002341333</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>78195.1609644261</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>90615.4327112397</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>106958.65283709</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>111613.571195993</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>128492.998657004</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>153479.995030091</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>172492.894367896</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>145147.059642189</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>181450.472756233</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>227017.492174369</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>203399.929905918</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>200610.382101562</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>219833.303258427</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-0.213715471255739</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-0.226651662849339</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-0.257272067753261</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>-0.344724648932419</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-0.397323744902328</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>-0.369002186307113</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-0.32929720945302</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>-0.311307039188014</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>-0.290070324701573</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>-0.233974381477481</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0.0294302752646813</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.0183592346428341</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.0797622460355429</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.00139609845219302</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>-0.0462500531353179</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.0827197921178</t>
+          <t>1855.79581990981</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.11656989727557</t>
+          <t>1880.79358164181</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.0575296108291</t>
+          <t>1948.74614569442</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.884016973125884</t>
+          <t>2209.32283597301</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.803923144947343</t>
+          <t>2403.6981576951</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.803793907242183</t>
+          <t>2288.50068048973</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.796431984708506</t>
+          <t>2154.59366511033</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.729660707770887</t>
+          <t>2102.17020530275</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.67990209409845</t>
+          <t>2033.02577367071</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.71694866647548</t>
+          <t>1854.64376550657</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0.75431847325941</t>
+          <t>1379.15856239004</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0.718390804597701</t>
+          <t>1404.23381332698</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.778331257783313</t>
+          <t>1325.01509104843</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>0.75295534974776</t>
+          <t>1426.74939828651</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.752709314500807</t>
+          <t>1498.58639950624</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>9577799418.22212</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>9839180719.3827</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>10874375239.0086</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>12400261592.17</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>13613175175.3952</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>12917513603.3245</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>12497873851.6962</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.231</t>
+          <t>12653092247.1954</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>11653088548.6136</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>10533066210.1001</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.243</t>
+          <t>8933649217.59741</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.267</t>
+          <t>9253502256.47465</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>8559388045.15067</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.269</t>
+          <t>9119701227.72423</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>9635564349.34393</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>9153881641.85169</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>9208245881.04167</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>10055262676.8742</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>11467443333.0878</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>12571575632.4387</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>11792986934.566</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>11522052209.8618</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.261</t>
+          <t>11614968421.7116</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>10663650684.2728</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.282</t>
+          <t>9516525185.22997</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>7452410166.9978</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>7977441293.61354</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>7184130783.81134</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.302</t>
+          <t>8086899252.18457</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.305</t>
+          <t>8424912933.75079</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.673</t>
+          <t>423917776.370425</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.675</t>
+          <t>630934838.341032</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.726</t>
+          <t>819112562.134451</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.903</t>
+          <t>932818259.082162</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1.037</t>
+          <t>1041599542.95647</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1.087</t>
+          <t>1124526668.75851</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>1.166</t>
+          <t>975821641.834427</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1038123825.48382</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>1.534</t>
+          <t>989437864.340801</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1.458</t>
+          <t>1016541024.87014</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1.428</t>
+          <t>1481239050.59961</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1.559</t>
+          <t>1276060962.86112</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1375257261.33933</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1032801975.53967</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>1.582</t>
+          <t>1210651415.59314</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.492</t>
+          <t>1459.18354170335</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.496</t>
+          <t>1454.50858888633</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.526</t>
+          <t>1447.38819526542</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.635</t>
+          <t>1447.71479696384</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.744</t>
+          <t>1448.65180406486</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.782</t>
+          <t>1444.0389260237</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.846</t>
+          <t>1445.09198368434</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1447.74982282069</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1.103</t>
+          <t>1443.30532737538</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.973</t>
+          <t>1420.70463761111</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.997</t>
+          <t>1419.74757851482</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1.129</t>
+          <t>1430.01447139925</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1.058</t>
+          <t>1430.70127074144</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>1.091</t>
+          <t>1428.74128091313</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>1.111</t>
+          <t>1429.27669890121</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>1454.54435798818</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>1449.72290236388</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>1444.56828310794</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.287</t>
+          <t>1445.18928130723</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.332</t>
+          <t>1446.18263981626</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>1442.44639421068</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.366</t>
+          <t>1445.06331968827</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.422</t>
+          <t>1449.05260651281</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.466</t>
+          <t>1445.40544503121</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.436</t>
+          <t>1425.74890408596</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.433</t>
+          <t>1423.79740125835</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.473</t>
+          <t>1435.08706260359</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.445</t>
+          <t>1436.24506035712</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.467</t>
+          <t>1435.01585285276</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.476</t>
+          <t>1435.52096450939</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>148837.696338658</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>147263.463228694</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>158228.068405386</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>189081.45053812</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>225907.905290161</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>238237.588130888</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>260765.435440502</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>310412.206089131</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>355816.190693633</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>283226.686708113</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>320856.211495521</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>375315.687189429</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>358324.93373082</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>370659.214860258</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>383013.801641112</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>4313568236.2063</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>4116770956.43835</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>4140481298.28244</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>4477668089.49876</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>4918576802.80719</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>4791925335.57809</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>5323360825.14869</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>5796038796.48924</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>5942027658.56916</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>5056074266.27028</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>5760915274.42008</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>7003617231.18823</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>6342075381.07469</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>6326820364.02952</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>7094688554.01458</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>132569.772631546</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>129403.33926409</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>133502.841905047</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>159671.234385717</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>193057.460034536</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>207089.116065347</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>227564.371144406</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>270252.339736816</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>324928.251913685</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>250494.17163031</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>291061.61017252</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>349374.263953052</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>332279.232746024</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>340359.528807885</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>355416.204903591</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>5976.432</t>
+          <t>11666649541.0934</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>6038.386</t>
+          <t>11413904608.0776</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>6005.793</t>
+          <t>11473498506.5398</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>6003.316</t>
+          <t>12907263257.3486</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>6066.013</t>
+          <t>14490364123.522</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>6138.331</t>
+          <t>14233918332.642</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>6217.963</t>
+          <t>14459167393.2456</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>6338.011</t>
+          <t>14961992087.6446</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>6436.824</t>
+          <t>15253538613.9745</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>6338.167</t>
+          <t>12801910813.262</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>6370.07</t>
+          <t>12432930677.493</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>6509.268</t>
+          <t>14392948720.0212</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>6537.069</t>
+          <t>13017330658.4897</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>6506.505</t>
+          <t>13232803630.0657</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>6531.333</t>
+          <t>14733316487.047</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>4972.022</t>
+          <t>16267.9237071124</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5046.563</t>
+          <t>17860.1239646035</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>5019.687</t>
+          <t>24725.2265003392</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>5016.187</t>
+          <t>29410.2161524025</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>5074.917</t>
+          <t>32850.4452556251</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>5141.645</t>
+          <t>31148.472065541</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>5207.967</t>
+          <t>33201.0642960964</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>5311.215</t>
+          <t>40159.8663523146</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>5394.065</t>
+          <t>30887.9387799477</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>5290.562</t>
+          <t>32732.5150778021</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>5320.788</t>
+          <t>29794.6013230017</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>5434.913</t>
+          <t>25941.4232363773</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>5449.255</t>
+          <t>26045.7009847962</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>5407.5</t>
+          <t>30299.6860523721</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>5424.248</t>
+          <t>27597.5967375216</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>11258.782</t>
+          <t>-7353081304.88708</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>10842.564</t>
+          <t>-7297133651.63926</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>10591.321</t>
+          <t>-7333017208.25734</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>11327.443</t>
+          <t>-8429595167.8498</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>12172.604</t>
+          <t>-9571787320.71482</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>11855.878</t>
+          <t>-9441992997.06392</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>12870.871</t>
+          <t>-9135806568.09686</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>13620.119</t>
+          <t>-9165953291.15532</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>14097.997</t>
+          <t>-9311510955.40534</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>13041.867</t>
+          <t>-7745836546.99175</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>14572.746</t>
+          <t>-6672015403.07291</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>17041.179</t>
+          <t>-7389331488.83295</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>15664.244</t>
+          <t>-6675255277.41503</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>15507.761</t>
+          <t>-6905983266.03614</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>13889.969</t>
+          <t>-7638627933.0324</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>95041.58024</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>94074.63004</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>101033.5776</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>122924.676</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>140586.07556</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>143645.0301</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>151527.44028</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>174404.21095</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>191440.7988</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>175222.58688</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>175008.83868</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>189563.1168</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>178245.82864</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>186114.48879</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>188841.983893675</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2698.292</t>
+          <t>0.119891015444705</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2710.764</t>
+          <t>0.115583770987731</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2660.55</t>
+          <t>0.116734316758501</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2638.34</t>
+          <t>0.117365872608589</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2643.238</t>
+          <t>0.122394591339535</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2622.959</t>
+          <t>0.12294283303961</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2658.026</t>
+          <t>0.12034155249256</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2693.045</t>
+          <t>0.120150735860958</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2722.109</t>
+          <t>0.111195474993641</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2659.827</t>
+          <t>0.105491449547407</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2670.522</t>
+          <t>0.111646222283102</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>2740.527</t>
+          <t>0.110786006596226</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2737.224</t>
+          <t>0.107604411082733</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>2720.216</t>
+          <t>0.105438461690416</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2720.836</t>
+          <t>0.108216000170323</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>118702.36504</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>121500.6784</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>133246.86</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>162403.44288</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>183766.3226</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>190165.16376</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>201197.344</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>231470.8716</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>262333.65296</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>250538.57884</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>242906.6853</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>266743.5312</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>254710.9576</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>269315.03982</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>271740.818543357</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>7163.601</t>
+          <t>132203.08804</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>7350.318</t>
+          <t>135708.20812</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>7636.713</t>
+          <t>148437.16752</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>8634.043</t>
+          <t>181166.31792</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>9440.116</t>
+          <t>205284.29992</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>9177.247</t>
+          <t>212888.27703</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>8761.701</t>
+          <t>226094.38528</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>8647.729</t>
+          <t>261023.37425</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>8564.086</t>
+          <t>295682.86632</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>7829.196</t>
+          <t>282246.42776</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>5885.795</t>
+          <t>273400.70184</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>6092.621</t>
+          <t>300115.2</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>5769.386</t>
+          <t>285579.43392</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>6140.795</t>
+          <t>302099.58675</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>5687.285</t>
+          <t>304972.340221593</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-30.59</t>
+          <t>672915.7481964</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-31.34</t>
+          <t>674669.00356</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-34.27</t>
+          <t>725912.5353456</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-41.9</t>
+          <t>902703.7073488</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-46.24</t>
+          <t>1036744.99887</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-43.97</t>
+          <t>1086579.02496</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-40.56</t>
+          <t>1166031.9008156</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-38.58</t>
+          <t>1340280.3365795</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-37.02</t>
+          <t>1533998.36396</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-32.43</t>
+          <t>1457587.6207948</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>-9.6</t>
+          <t>1428485.63067</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>-10.8</t>
+          <t>1558587.324384</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>-5.55</t>
+          <t>1484992.3968</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>-11.94</t>
+          <t>1559776.95144</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>1581773.66498213</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.309</t>
+          <t>163688.764736071</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.291</t>
+          <t>169055.645340854</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.206</t>
+          <t>171552.749950655</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1.071</t>
+          <t>171050.840578795</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1.002</t>
+          <t>172371.340410584</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.942</t>
+          <t>175692.475488236</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.912</t>
+          <t>180582.482545488</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.822</t>
+          <t>187285.068090498</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.764</t>
+          <t>193845.727166498</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.852</t>
+          <t>190919.974303546</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>0.914</t>
+          <t>190475.13632</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>0.903</t>
+          <t>195230.81898638</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>0.891</t>
+          <t>197201.253088949</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>0.866</t>
+          <t>199472.789963156</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>0.732</t>
+          <t>200280.095916704</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>147181.005307898</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>151837.154604761</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>154268.649951986</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>153691.648067614</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>154688.429789492</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>157146.832105325</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>160824.411997213</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>166233.892901662</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>172234.604049527</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>169438.682796024</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>169230.3044</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>173397.488311908</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>176297.502632207</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>178401.762307325</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>179121.031650803</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>80676.55236</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>77980.7876</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>84738.90384</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>105946.60832</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>126891.98046</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>133587.10365</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>140322.0892</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>161035.6687</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>170573.67672</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>153763.03096</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>159485.02425</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>172669.6656</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>159791.73232</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>164460.48234</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>171173.219199119</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>4972022000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>5046563000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>5019687000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>5016187000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>5074917000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>5141645000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>5207967000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>5311215000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>5394065000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>5290562000</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>5320788000</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>5434913000</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>5449255000</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>5407500000</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>5424248000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>5976431858.10185</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>6038385832.92602</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>6005792637.02126</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>6003316274.55024</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>6066013082.7093</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>6138330630.56357</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>6217962958.28666</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>6338011195.62639</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>6436824068.35747</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>6338166753.11412</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>6370069573.22985</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>6509267898.55738</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>6537069392.21542</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>6506505378.41969</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>6531333284.32484</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2698291872.46098</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2710763616.60758</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2660549892.99879</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2638340003.83444</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2643237525.1341</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2622958582.6215</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>2658026200.31574</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>2693045274.69151</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>2722108969.92773</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2659827430.59279</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>2670521568.2849</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>2740526915.24889</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>2737224263.32177</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>2720215906.53791</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2720835784.01712</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>4108800</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4165200</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>4157500</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>4154000</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>4194500</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>4255500</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>4302900</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>4373900</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>4453300</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>4445500</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>4474000</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>4535800</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>4551500</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>4534100</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>4549800</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>3407400</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3469600</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>3468100</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>3464900</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>3503200</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>3560600</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>3603900</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>3668600</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>3737300</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>3723900</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>3747700</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>3800600</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>3808800</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>3784800</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>3795100</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>5976431858.10185</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>6038385832.92602</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>6005792637.02126</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>6003316274.55024</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>6066013082.7093</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>6138330630.56357</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>6217962958.28666</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>6338011195.62639</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>6436824068.35747</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>6338166753.11412</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>6370069573.22985</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>6509267898.55738</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>6537069392.21542</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>6506505378.41969</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>6531333284.32484</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>4972022000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5046563000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>5019687000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>5016187000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>5074917000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>5141645000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>5207967000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>5311215000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>5394065000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>5290562000</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>5320788000</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>5434913000</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>5449255000</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>5407500000</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>5424248000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>492090.93976</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>496082.87072</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>525752.27616</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>635131.35728</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>743575.05908</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>781713.06642</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>845735.37092</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>979721.79725</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>1103384.30564</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>972813.99996</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>997284.73671</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>1129381.6608</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1058281.92272</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>1091329.25382</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>1110756.4587</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>212879.6404</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>213688.99572</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>233176.07136</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>287112.92624</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>332176.28038</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>346475.38068</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>366416.47448</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>422059.04295</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>466256.54304</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>436009.45872</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>432885.72609</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>472784.8656</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>445371.16624</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>466560.06909</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>476145.5594</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>835192.387342103</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>848072.371855903</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>845468.221181167</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>864842.242318948</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>881481.125702826</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>898816.058414313</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>927854.332874125</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>955332.944505346</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>992014.099494646</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>986724.612013183</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>995209.57116</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>1008232.1898279</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1016949.25921611</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>1021122.35535113</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>1025095.12615137</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW16</t>
